--- a/docs/暮らし帳_詳細設計書.xlsx
+++ b/docs/暮らし帳_詳細設計書.xlsx
@@ -18,9 +18,12 @@
     <sheet name="テーブル一覧" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="テーブル定義" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="環境変数" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ファイル処理" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="起動時フロー" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="画面遷移フロー" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'改訂履歴'!$A$1:$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'改訂履歴'!$A$1:$C$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'システム構成'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'機能一覧'!$A$1:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'画面一覧'!$A$1:$D$17</definedName>
@@ -30,6 +33,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'テーブル一覧'!$A$1:$D$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'テーブル定義'!$A$1:$H$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'環境変数'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ファイル処理'!$A$1:$C$101</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'ファイル処理'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'起動時フロー'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'起動時フロー'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'画面遷移フロー'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'画面遷移フロー'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,13 +522,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F18"/>
+  <dimension ref="B1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -527,6 +539,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -534,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -566,7 +580,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -606,6 +620,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="20" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -618,6 +633,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B4:F4"/>
@@ -8055,13 +8071,2191 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>ファイル</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/__root.tsx</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>全画面の親。起動時にセッションとメニュー下の表示設定を取り、テーマ・読み込み表示・iPhoneの長押し抑止を載せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/index.tsx</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>未ログインはログイン画面。ログイン後はメニューと、表示オンの下部コンテンツだけを出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/login.tsx</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ログイン画面のルート</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/forgot-password.tsx</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>再設定メールの送信画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/reset-password.tsx</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>メールリンクから新しいパスワードを保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/password.tsx</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>ログイン中のパスワード変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/calorie.tsx</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>わんカロリー。遷移時の loader で当日の状態を取り、餌・体重・グラフ・犬の切替を置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/smoking.tsx</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>喫煙管理。画面表示後に状態を取得し、減算・上限・バッチを切り替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/walk.tsx</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ配下をログイン必須にする枠</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/walk.index.tsx</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>カード一覧。検索ボタンまで絞り込まず、サムネイルは一覧のあと別取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/walk.new.tsx</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>カード追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/walk.$id.edit.tsx</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>カード編集。1件を読んでフォームに渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/walk.logs.tsx</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログ配下の枠</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/walk.logs.index.tsx</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>GPXの取り込みとログ一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/walk.logs.$id.tsx</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>ログ詳細。地図、削除、前と次</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/vet.tsx</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>通院配下をログイン必須にする枠</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/vet.index.tsx</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>次の予約、年ごとの履歴、先生へのメモ、TOPへ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/vet.new.tsx</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>予定または記録の追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/vet.$id.edit.tsx</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>1件を読んで編集する</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/cup.tsx</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>カップ麺画面のルート</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/api/auth/$.ts</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>better-auth のログイン・セッションAPIの受け口</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/api/blob/upload.ts</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモ画像を Vercel Blob へ保存する受け口</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/api/walk/image.ts</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ画像の取得。Blobのトークンをブラウザに出さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/api/cup/image.ts</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>カップ麺画像の保存と取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/api/cron/calorie-summary.ts</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ。認証のあと喫煙リセットとカロリー再集計を行い cron_runs に残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>src/components/app-shell.tsx</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>共通ヘッダー。タイトルでメニューへ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>src/components/nav-busy.tsx</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>リンクと検索を押した瞬間に「読み込み中」を出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>src/components/protected.tsx</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>未ログインをログインへ戻す。確認中はスプラッシュ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>src/components/login-form.tsx</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>ログイン、新規登録、再設定への導線</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>src/components/account-chip.tsx</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>右上の丸。メール、テーマ、表示設定、パスワード、サインアウト確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>src/components/desk-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>メニュー下。表示設定を見てから各コンテンツを取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>src/components/theme-provider.tsx</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>保存済みテーマを画面へ適用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>src/components/theme-settings.tsx</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>テーマの選択</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>src/components/theme-motif.tsx</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>季節テーマの花と果物</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>画面部品</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>src/components/ui/busy-overlay.tsx</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>「読み込み中」などの全面オーバーレイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>src/components/calorie/today-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>カロリー加算、今日の記録、体重、棒グラフ。日付移動は先に読み込み中</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>src/components/calorie/trend-chart.tsx</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>日週月年の推移。目安線、期間のスライド、今日へ移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>src/components/calorie/plan-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>目安カロリーのプラン保存。保存時に期間の目安をDBへ書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>src/components/calorie/foods-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>フードの登録・編集・削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>src/components/calorie/profile-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>愛犬の追加と理想体重などのプロフィール</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>src/components/calorie/dog-switcher.tsx</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>多頭の切替。選んだ犬の当日データを取り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/calorie/api.ts</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>カロリーのサーバー処理。加算、体重、当日取得、グラフ取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/calorie/formula.ts</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>カロリー計算、小数第1位切り捨て、日本時間の今日、2週間ロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/calorie/summary.ts</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>週月年の集計、目安の保存、グラフ用の読み分け</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/calorie/saburo.ts</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>摂取量に応じた体型画像の段階</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>わんカロリー</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/calorie/types.ts</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>カロリー画面の型</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>src/components/smoking/count-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>残数の減算、修正、前回吸った時刻とリセット時刻</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>src/components/smoking/master-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>1日の上限本数の保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>src/components/smoking/badge-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>達成バッチの表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/smoking/api.ts</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>残数更新、上限保存、0時のリセットとバッチ確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/smoking/period.ts</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>日本時間の日付だけでリセットするか判定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/smoking/badges.ts</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>ナイス、ベリーナイス、日数・本数のバッチ判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/smoking/saburo.ts</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>残数に応じた表情画像の段階</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>喫煙</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/smoking/types.ts</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>喫煙画面の型</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>src/components/walk/memo-form.tsx</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>追加と編集のフォーム。画像の選択、貼り付け、保存、削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>src/components/walk/memo-card.tsx</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>一覧の1枚。サムネ、虹、今日会った</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>src/components/walk/memo-toolbar.tsx</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>検索語はボタンを押すまで反映しない。並びと犬種は即時</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>src/components/walk/image-lightbox.tsx</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>画像の全体表示。縦横で画面に合わせ、閉じる</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>src/components/walk/walk-subnav.tsx</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>カードと散歩ログの切替</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>src/components/walk/track-map.tsx</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>GPXの軌跡を Leaflet で描く</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/walk/api.ts</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>カードの取得・保存・削除、サムネイル、犬種と毛色</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/walk/filter.ts</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>名前検索。ひらがなとカタカナを区別しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/walk/image.ts</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>アップロード前の縮小。失敗時はそのまま送る</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/walk/thumbs.ts</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>一覧用サムネのURLをカードへ当てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/walk/age.ts</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>生年月日から満年齢。未来日の判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/walk/types.ts</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>カードと検索条件の型</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログ</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/walk-log/gpx.ts</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>GPXから開始、距離、時間、軌跡を読む</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>散歩ログ</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/walk-log/api.ts</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>ログの保存、一覧、詳細、削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログ</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/walk-log/format.ts</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>距離と時間の表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>通院</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>src/components/vet/visit-form.tsx</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>予定と記録の入力。先生メモのコピー。保存時の重複予定削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>通院</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>src/components/vet/doctor-memo.tsx</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>先生へ伝えるメモ。履歴は持たず1件を上書き</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>通院</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/vet/api.ts</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>通院の一覧・保存・削除と先生メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>通院</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/vet/types.ts</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>通院の型</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>カップ麺</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>src/components/cup/cup-app.tsx</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>品名と在庫の一覧、追加、編集、削除、画像</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>カップ麺</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/cup/api.ts</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>品名と在庫のサーバー処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/desk/api.ts</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>何の日、格言、小話、占い、豆知識、犬ネタの取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/desk/settings.ts</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>表示オンオフの読み書き。初期は全部オフ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/desk/visibility.ts</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>どの枠を出すかの判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/desk/dog-facts.ts</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>豆知識の文面と参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/desk/dog-news.ts</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>犬の話題をWebから取り、日次でキャッシュ</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/desk/countries.ts</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>何の日で使う国・祝日</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="34" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/desk/types.ts</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>メニュー下の型</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/auth/server.ts</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>better-auth のサーバー設定。Postgres と再設定メール</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/auth/client.ts</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>ブラウザ側のログインクライアント</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="34" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/auth/verify.server.ts</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>リクエストのセッションからユーザーを取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="34" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/auth/use-current-user.ts</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>画面がログイン状態を見るフック</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="34" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/auth/middleware.ts</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>サーバー処理をログイン必須にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/auth/gates.tsx</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>未ログインをログイン画面へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/auth/send-reset-mail.ts</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Resend で再設定メールを送る。有効期限1時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="34" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/auth/email-password.ts</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>メール形式とパスワードのチェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="34" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/db.ts</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>DB接続。本番は Supabase。未設定時だけ PGLite を起動時に作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="34" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/postgres-url.ts</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Supabase の 5432 をサーバーレス用の 6543 に変える</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="34" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/cron-log.ts</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>cron_runs の開始、ログ追記、終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="34" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/theme.ts</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>テーマ一覧と、描画前に色を当てるスクリプト</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="34" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/app-meta.ts</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>アプリ名とメニュー定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="34" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/menu-layout.ts</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>メニューを一覧とアイコンのどちらで出すか</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="34" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>src/router.tsx</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>ルーター。遷移の待ち表示は0ミリ秒で始める</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="34" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>ビルド</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>scripts/migrate.mjs</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>デプロイ時に未適用の migrations/*.sql を本番DBへ実行する</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="34" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>ビルド</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>scripts/migration-plan.mjs</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>適用済みと未適用のマイグレーションを分ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="34" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>ビルド</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>vite.config.ts</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Vite、Nitro、Vercel、毎日 UTC 15:00 の Cron 定義</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C101"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L暮らし帳　詳細設計書</oddHeader>
+    <oddFooter>&amp;RPage &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>ブラウザがページを要求する。サーバーは head に CSS、アプリ名、テーマ色を付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>head 内のスクリプトが localStorage のテーマを、画面が見える前に html へ当てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>セッション</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ルートの beforeLoad がセッションを読む。ユーザーがいれば id とメールだけを画面へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>表示設定</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>ログイン済みなら user_settings を読む。読めないときはメニュー下を出さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>データベース</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>本番は初回のSQLで Supabase へ接続する。テーブル作成はデプロイ時の migrate が済ませている</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>ローカル</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>DATABASE_URL が無いときだけ PGLite を開き、migrations/*.sql を起動時に適用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ハイドレート</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ブラウザが画面を受け取る。タッチ端末では長押しのプレビューとドラッグを止める</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>読み込み表示</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>NavBusy がリンクと検索ボタンの監視を始める</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>メニュー判定</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>セッション確認中はスプラッシュ。未ログインはログイン画面。ログイン済みはメニュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>メニュー下</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>表示がオンの枠だけ、そのあとで中身を取りに行く。オフの枠は取得しない</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L暮らし帳　詳細設計書</oddHeader>
+    <oddFooter>&amp;RPage &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>押下</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>アプリ内リンク、または「検索」ボタンを押す。修飾キーや別タブ、ダウンロードは対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>先に表示</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>遷移や検索の結果より先に、画面全体へ「読み込み中」を描く</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ルーター</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>TanStack Router がパスと検索条件を変える。待ち時間のしきい値は 0 ミリ秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>loader</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>遷移先に loader があるとき（わんカロリー）は、当日データを取り終わるまで画面を替えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>描画</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>遷移先を描く。ログイン必須の画面は Protected がセッションを見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>未ログイン</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>セッションが無いときはログイン画面へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>後読み</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>loader が無い画面は、描いたあと useEffect でサーバー処理を呼ぶ。届くまで各画面の「読み込み中」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>検索</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>お散歩メモの検索は、取得済みのカードをブラウザで絞り込む。並びと犬種の変更もURLへ残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>遷移先の描画が終わったら共通の「読み込み中」を消す。20秒経っても消えなければ強制で消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>戻る</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>ヘッダーの「暮らし帳」はメニュー（/）へ戻る。このときも同じ遷移の流れ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L暮らし帳　詳細設計書</oddHeader>
+    <oddFooter>&amp;RPage &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8103,8 +10297,25 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>ファイル処理、起動時フロー、画面遷移フローを追加</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
+  <autoFilter ref="A1:C3"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/docs/暮らし帳_詳細設計書.xlsx
+++ b/docs/暮らし帳_詳細設計書.xlsx
@@ -23,19 +23,19 @@
     <sheet name="画面遷移フロー" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'改訂履歴'!$A$1:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'改訂履歴'!$A$1:$C$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'システム構成'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'機能一覧'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'画面一覧'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'機能一覧'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'画面一覧'!$A$1:$D$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'画面遷移'!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'処理設計'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'処理設計'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'バッチ処理'!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'テーブル一覧'!$A$1:$D$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'テーブル定義'!$A$1:$H$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'環境変数'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ファイル処理'!$A$1:$C$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ファイル処理'!$A$1:$C$115</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'ファイル処理'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'起動時フロー'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'起動時フロー'!$A$1:$C$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'起動時フロー'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'画面遷移フロー'!$A$1:$C$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'画面遷移フロー'!$1:$1</definedName>
@@ -522,16 +522,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:F19"/>
+  <dimension ref="B4:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -539,7 +536,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -547,7 +543,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -580,7 +575,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -620,11 +615,10 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="64" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>本書は、2026-10-01 時点のソースと本番データベースのテーブル定義に基づく。
+          <t>テーブル定義は 2026-10-01 時点の本番データベースに基づく。画面と遷移は 2026-10-14 の実装に合わせた。
 日時列（timestamptz）は UTC で保存する。日付だけの列（date）は日本時間の暦日である。
 画面項目は主要画面に限る。認証テーブルのパスワード列は値を本書に記載しない。</t>
         </is>
@@ -633,7 +627,6 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B4:F4"/>
@@ -8077,7 +8070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8115,7 +8108,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>全画面の親。起動時にセッションとメニュー下の表示設定を取り、テーマ・読み込み表示・iPhoneの長押し抑止を載せる</t>
+          <t>全画面の親。セッションとメニュー下の表示設定は初回だけ取り、以降の遷移ではブラウザに残したものを使う。テーマとiPhoneの長押し抑止もここ。</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8125,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>未ログインはログイン画面。ログイン後はメニューと、表示オンの下部コンテンツだけを出す</t>
+          <t>未ログインはログイン画面。ログイン後はメニューと、表示オンの下部コンテンツ。表示後に各メニュー先を先読みする。</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8210,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>わんカロリー。遷移時の loader で当日の状態を取り、餌・体重・グラフ・犬の切替を置く</t>
+          <t>ごはん、体重、おくすり。loader は使わない。暮らし帳の日付と記録を使う。プランとフードはプロフィールから開く。</t>
         </is>
       </c>
     </row>
@@ -8246,12 +8239,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>src/routes/walk.tsx</t>
+          <t>src/routes/dogfriend.tsx</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>お散歩メモ配下をログイン必須にする枠</t>
+          <t>おさんぽメモ配下をログイン必須にする枠。パスは /dogfriend</t>
         </is>
       </c>
     </row>
@@ -8263,12 +8256,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>src/routes/walk.index.tsx</t>
+          <t>src/routes/dogfriend.index.tsx</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>カード一覧。検索ボタンまで絞り込まず、サムネイルは一覧のあと別取得</t>
+          <t>カード一覧。検索ボタンまで絞り込まず、サムネイルは一覧のあと別取得。戻ったときは残している一覧を出す。</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8273,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>src/routes/walk.new.tsx</t>
+          <t>src/routes/dogfriend.new.tsx</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -8297,7 +8290,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>src/routes/walk.$id.edit.tsx</t>
+          <t>src/routes/dogfriend.$id.edit.tsx</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8314,12 +8307,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>src/routes/walk.logs.tsx</t>
+          <t>src/routes/dogwalklogs.tsx</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>散歩ログ配下の枠</t>
+          <t>おさんぽログ配下をログイン必須にする枠。パスは /dogwalklogs</t>
         </is>
       </c>
     </row>
@@ -8331,12 +8324,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>src/routes/walk.logs.index.tsx</t>
+          <t>src/routes/dogwalklogs.index.tsx</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>GPXの取り込みとログ一覧</t>
+          <t>GPXの取り込みとログ一覧。戻ったときは残している一覧を出す。</t>
         </is>
       </c>
     </row>
@@ -8348,12 +8341,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>src/routes/walk.logs.$id.tsx</t>
+          <t>src/routes/dogwalklogs.$id.tsx</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>ログ詳細。地図、削除、前と次</t>
+          <t>ログ詳細。地図、削除、前と次。一覧へは画面下に固定。一覧にあれば名前と距離を先に出す。</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8550,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>リンクと検索を押した瞬間に「読み込み中」を出す</t>
+          <t>リンクと検索を監視する。移動が0.2秒を超えたときだけ「読み込み中」を出す。20秒で消す。</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8703,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>カロリー加算、今日の記録、体重、棒グラフ。日付移動は先に読み込み中</t>
+          <t>カロリー加算、今日の記録、体重、おくすりへの入口、棒グラフ。日付は先に画面を替え、記録はあとから取る。</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9740,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>ルーター。遷移の待ち表示は0ミリ秒で始める</t>
+          <t>ルーター。遷移の待ち表示の最小時間は0。画面に見えているリンクは、部品を先に読む。</t>
         </is>
       </c>
     </row>
@@ -9802,8 +9795,246 @@
         </is>
       </c>
     </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>src/routes/dogwalklogs.month.$yearMonth.tsx</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>月の地図。700m四方で軌跡を分ける。一覧へは画面下に固定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>src/components/page-heading.tsx</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>各画面の先頭に出す機能名。大きさは全画面で同じ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>src/components/list-back-bar.tsx</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>画面下に固定する「一覧へ」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>src/components/calorie/menu-board.tsx</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>犬と人のメニュー。絵のタップで切り替え、歯車はプロフィール。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>src/components/calorie/medicine-panel.tsx</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>おくすりの投与。管理は画面下の固定ボタンで、登録・編集・削除を開く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/calorie/held.ts</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>暮らし帳とわんカロリーで共有する、今の日付と記録。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/route-context.ts</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>ログインとメニュー下の表示設定。遷移のたびには取り直さない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/warm-menus.ts</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>暮らし帳表示中に、メニュー先の画面とデータを先読みする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/walk/held.ts</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>おさんぽメモ一覧の控え。保存と削除のあとだけ消す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/walk-log/held.ts</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>おさんぽログ一覧の控え。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/vet/held.ts</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>通院一覧の控え。保存と削除のあとだけ消す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/smoking/held.ts</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>喫煙画面の控え。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/cup/held.ts</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>カップ麺の控え。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/desk/held.ts</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>メニュー下に出した内容の控え。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C101"/>
+  <autoFilter ref="A1:C115"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -9823,7 +10054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9895,7 +10126,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>ルートの beforeLoad がセッションを読む。ユーザーがいれば id とメールだけを画面へ渡す</t>
+          <t>ルートの beforeLoad がセッションを読む。ブラウザに残っていればサーバーへ聞かない。ユーザーがいれば id とメールだけを画面へ渡す。</t>
         </is>
       </c>
     </row>
@@ -9912,7 +10143,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>ログイン済みなら user_settings を読む。読めないときはメニュー下を出さない</t>
+          <t>ログイン済みなら user_settings を初回だけ読む。以降の遷移では残した値を使う。読めないときはメニュー下を出さない。</t>
         </is>
       </c>
     </row>
@@ -9980,7 +10211,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>NavBusy がリンクと検索ボタンの監視を始める</t>
+          <t>NavBusy がリンクと検索ボタンの監視を始める。押した瞬間には出さない。</t>
         </is>
       </c>
     </row>
@@ -10018,8 +10249,25 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>先読み</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>メニューを出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺と、各画面の部品を裏で読む。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:C12"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -10077,7 +10325,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>アプリ内リンク、または「検索」ボタンを押す。修飾キーや別タブ、ダウンロードは対象外</t>
+          <t>アプリ内リンク、または「検索」ボタンを押す。修飾キーや別タブ、ダウンロードは対象外。</t>
         </is>
       </c>
     </row>
@@ -10089,12 +10337,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>先に表示</t>
+          <t>待ち</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>遷移や検索の結果より先に、画面全体へ「読み込み中」を描く</t>
+          <t>0.2秒以内に描けるときは「読み込み中」を出さない。超えたときだけ画面全体へ出す。</t>
         </is>
       </c>
     </row>
@@ -10106,12 +10354,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ルーター</t>
+          <t>確認の省略</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>TanStack Router がパスと検索条件を変える。待ち時間のしきい値は 0 ミリ秒</t>
+          <t>ログインとメニュー下の表示設定は、ブラウザに残っていればサーバーへ聞かない。</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10371,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>loader</t>
+          <t>引き渡し</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>遷移先に loader があるとき（わんカロリー）は、当日データを取り終わるまで画面を替えない</t>
+          <t>ごはん、体重、おくすりは、暮らし帳の日付と記録を渡す。このときは取り直さない。</t>
         </is>
       </c>
     </row>
@@ -10140,12 +10388,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>描画</t>
+          <t>既読</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>遷移先を描く。ログイン必須の画面は Protected がセッションを見る</t>
+          <t>おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺は、先読みか前回の内容があればそれを出す。</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10405,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>未ログイン</t>
+          <t>未取得</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>セッションが無いときはログイン画面へ戻す</t>
+          <t>まだ無い画面は、描いたあとでサーバー処理を呼ぶ。届くまでその画面の「読み込み中」。</t>
         </is>
       </c>
     </row>
@@ -10174,12 +10422,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>後読み</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>loader が無い画面は、描いたあと useEffect でサーバー処理を呼ぶ。届くまで各画面の「読み込み中」</t>
+          <t>セッションが無いときはログイン画面へ戻す。</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10444,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>お散歩メモの検索は、取得済みのカードをブラウザで絞り込む。並びと犬種の変更もURLへ残す</t>
+          <t>おさんぽメモの検索は、取得済みのカードをブラウザで絞り込む。並びと犬種の変更もURLへ残す。</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10461,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>遷移先の描画が終わったら共通の「読み込み中」を消す。20秒経っても消えなければ強制で消す</t>
+          <t>遷移先の描画が終わったら共通の「読み込み中」を消す。20秒経っても消えなければ強制で消す。</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10478,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>ヘッダーの「暮らし帳」はメニュー（/）へ戻る。このときも同じ遷移の流れ</t>
+          <t>ヘッダーの「暮らし帳」はメニュー（/）へ戻る。日付と記録は残したままなので、次の移動でも使える。</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10314,8 +10562,25 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>メニューを犬と人に分け、日付と記録を画面へ渡す。一覧は戻ったとき取り直さない。ログイン確認は遷移のたびには行わない。メニュー表示中に先読みする。おくすりの管理は画面下に固定。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C3"/>
+  <autoFilter ref="A1:C4"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -10495,7 +10760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10548,7 +10813,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>F02</t>
@@ -10561,7 +10826,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>わんカロリー、喫煙管理、お散歩メモ、通院履歴、カップ麺。配色テーマと表示のオンオフ</t>
+          <t>犬の絵と人の絵で切り替える。犬はごはん、体重、おくすり、おさんぽメモ、おさんぽログ、通院履歴。人は喫煙管理、カップ麺。日付は暮らし帳とごはん・体重・おくすりで共有。プランとフードはプロフィールから開く。</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -10570,7 +10835,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>F03</t>
@@ -10578,12 +10843,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>わんカロリー</t>
+          <t>ごはん・体重・おくすり</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>フード選択と数量からカロリーを加算。定番、体重、グラフ</t>
+          <t>ごはんは登録フードと数量からカロリーを加算する。体重、おくすり、定番、グラフ。暮らし帳で持っている日付と記録をそのまま開く。おくすりの管理は画面下の固定ボタン。</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -10768,8 +11033,30 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>画面の先読み</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>暮らし帳を出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺を裏で読む。一度開いた内容は、戻ったときに再取得しない。ログインと表示設定も、遷移のたびには取り直さない。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>なし（ブラウザ内）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:D13"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -10789,7 +11076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10820,7 +11107,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>S01</t>
@@ -10838,7 +11125,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>メールアドレス、テーマ、メニュー。下部コンテンツは設定がオンのものだけ</t>
+          <t>犬と人の絵、各メニュー、日付。下部コンテンツは設定がオンのものだけ。歯車はプロフィール</t>
         </is>
       </c>
     </row>
@@ -10930,7 +11217,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>S06</t>
@@ -10943,12 +11230,12 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>わんカロリー</t>
+          <t>ごはん・体重・おくすり</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>犬の切替、カロリーを足す、今日の記録、体重、棒グラフ、推移グラフ</t>
+          <t>日付はメニューと同期。おくすりの管理は画面下に固定。プランとフードはプロフィールから</t>
         </is>
       </c>
     </row>
@@ -10974,7 +11261,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>S08</t>
@@ -10982,21 +11269,21 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>/walk</t>
+          <t>/dogfriend</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>お散歩メモ一覧</t>
+          <t>おさんぽメモ一覧</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>名前検索、並び順、犬種、サムネイル、今日会った</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+          <t>名前検索、並び順、犬種、サムネイル、今日会った。戻ったときは取り直さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>S09</t>
@@ -11004,12 +11291,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>/walk/new</t>
+          <t>/dogfriend/new</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>お散歩メモ追加</t>
+          <t>おさんぽメモ追加</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -11018,7 +11305,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>S10</t>
@@ -11026,21 +11313,21 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>/walk/$id/edit</t>
+          <t>/dogfriend/$id/edit</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>お散歩メモ編集</t>
+          <t>おさんぽメモ編集</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>S09 と同じ。削除あり。一覧へ・保存・キャンセルは固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
+          <t>S09 と同じ。削除あり。一覧へ・保存・キャンセルは画面下に固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>S11</t>
@@ -11048,21 +11335,21 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>/walk/logs</t>
+          <t>/dogwalklogs</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>散歩ログ一覧</t>
+          <t>おさんぽログ一覧</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>GPX 取り込み</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+          <t>GPX 取り込み。戻ったときは取り直さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>S12</t>
@@ -11070,17 +11357,17 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>/walk/logs/$id</t>
+          <t>/dogwalklogs/$id</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>散歩ログ詳細</t>
+          <t>おさんぽログ詳細</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>地図、距離、時間。前・次</t>
+          <t>地図、距離、時間。前・次。一覧へは画面下に固定</t>
         </is>
       </c>
     </row>
@@ -11172,8 +11459,30 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>/dogwalklogs/month/$yearMonth</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>月の地図</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>その月の軌跡。700m四方で地図を分ける。一覧へは画面下に固定</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D17"/>
+  <autoFilter ref="A1:D18"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -11255,136 +11564,136 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>メニュー</t>
+          <t>犬の絵</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>各メニュー</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>わんカロリー / 喫煙管理 / お散歩メモ / 通院履歴 / カップ麺</t>
+          <t>次の犬、最後に人。3匹以上は「人」で人のメニューへ直接</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>わんカロリー</t>
+          <t>犬のメニュー</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>お散歩メモ、通院のアイコン</t>
+          <t>ごはん・体重・おくすり</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>お散歩メモ、通院履歴</t>
+          <t>/calorie。日付と記録を渡す。取り直さない</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>お散歩メモ</t>
+          <t>犬のメニュー</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>追加</t>
+          <t>おさんぽメモ、おさんぽログ、通院履歴</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>追加画面</t>
+          <t>各一覧。先読み済みならそのまま出す</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>お散歩メモ</t>
+          <t>人のメニュー</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>カード</t>
+          <t>喫煙管理、カップ麺</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>編集画面</t>
+          <t>各画面。先読み済みならそのまま出す</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>お散歩メモ</t>
+          <t>歯車</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>散歩ログ</t>
+          <t>プロフィール</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ログ一覧、詳細</t>
+          <t>/calorie のプロフィール。そこからプランとフード</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>通院履歴</t>
+          <t>おくすり</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>予定 / 記録</t>
+          <t>管理</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>追加画面</t>
+          <t>画面下の固定ボタン。登録、編集、削除</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>通院履歴</t>
+          <t>おさんぽログの詳細・月の地図</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>行</t>
+          <t>一覧へ</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>編集画面</t>
+          <t>画面下に固定。ログ一覧へ戻る</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>いずれかのリンクまたは検索</t>
+          <t>アプリ内リンク、または検索</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>押下直後</t>
+          <t>0.2秒より長くかかるときだけ</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>先に「読み込み中」を出す</t>
+          <t>「読み込み中」。すぐ描ける移動では出さない</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11502,7 +11811,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>P05</t>
@@ -11515,7 +11824,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>1. 初期表示は当日分を優先し、グラフは開くまで取らない。2. 締まった週・月・年は calorie_period_stats を読む。3. 今日を含む期間だけ明細を足す。</t>
+          <t>1. 初期表示は当日分を優先し、グラフは開くまで取らない。2. 締まった週・月・年は calorie_period_stats を読む。3. 今日を含む期間だけ明細を足す。4. 日付をタップした値は、グラフ上部へカロリー、体重、距離を横一列で出す。</t>
         </is>
       </c>
     </row>
@@ -11604,8 +11913,42 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>日付と記録の引き渡し</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1. 暮らし帳で読んだ犬・日付・食事・体重・おくすりをブラウザに残す。2. ごはん、体重、おくすりを開くときはそれを渡す。3. どちらかで日付や保存内容が変われば、残している内容も更新する。4. ブラウザを開き直したときだけ取り直す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>先読みと再表示</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1. 暮らし帳を出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺を裏で読む。2. 戻ったときは残している内容を出す。3. 保存、削除、取り込みのあとだけ取り直す。4. ログインとメニュー下の表示設定は、最初の1回だけサーバーへ聞く。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:C13"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/docs/暮らし帳_詳細設計書.xlsx
+++ b/docs/暮らし帳_詳細設計書.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7866,6 +7866,678 @@
         </is>
       </c>
       <c r="H221" s="8" t="inlineStr"/>
+    </row>
+    <row r="222" ht="32" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>memos</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>お散歩メモ</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>prev_last_met_on</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>最後に会った日の一つ前。戻すと入れ替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="32" customHeight="1">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>dogs</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>愛犬</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>portrait_id</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E223" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F223" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G223" s="8" t="inlineStr">
+        <is>
+          <t>chihuahua-smooth-wr</t>
+        </is>
+      </c>
+      <c r="H223" s="8" t="inlineStr">
+        <is>
+          <t>メニューの犬の絵</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="32" customHeight="1">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>user_settings</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>メニュー下の表示設定</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t>person_portrait</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="H224" s="7" t="inlineStr">
+        <is>
+          <t>人の絵</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="32" customHeight="1">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>app_settings</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>アプリ共通の設定</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G225" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H225" s="8" t="inlineStr">
+        <is>
+          <t>例: medicine_added_on</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="32" customHeight="1">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>app_settings</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>アプリ共通の設定</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>日付など</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="32" customHeight="1">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G227" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H227" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="32" customHeight="1">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C228" s="7" t="inlineStr">
+        <is>
+          <t>dog_id</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H228" s="7" t="inlineStr">
+        <is>
+          <t>dogs.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="32" customHeight="1">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G229" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H229" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="32" customHeight="1">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr">
+        <is>
+          <t>due_time</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>予定時刻。空なら案内しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="32" customHeight="1">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicine_doses</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>おくすりの投与日</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>medicine_id</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G231" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H231" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicines.id。日ごとに1件</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="32" customHeight="1">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicine_doses</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>おくすりの投与日</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr">
+        <is>
+          <t>given_on</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H232" s="7" t="inlineStr">
+        <is>
+          <t>日本時間の暦日</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="32" customHeight="1">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G233" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H233" s="8" t="inlineStr">
+        <is>
+          <t>ブラッシング、歯磨きなど</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="32" customHeight="1">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="inlineStr">
+        <is>
+          <t>last_done_on</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H234" s="7" t="inlineStr">
+        <is>
+          <t>最後にやった日だけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="32" customHeight="1">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>year_month</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E235" s="8" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F235" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G235" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H235" s="8" t="inlineStr">
+        <is>
+          <t>user_id と組む</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="32" customHeight="1">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>regions</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H236" s="7" t="inlineStr">
+        <is>
+          <t>700m四方ごとの軌跡</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="32" customHeight="1">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>cell_m</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G237" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H237" s="8" t="inlineStr">
+        <is>
+          <t>区切りの一辺。いまは700</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H221"/>
@@ -8070,7 +8742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8210,7 +8882,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ごはん、体重、おくすり。loader は使わない。暮らし帳の日付と記録を使う。プランとフードはプロフィールから開く。</t>
+          <t>ごはん、体重、お世話。loader は使わない。暮らし帳の日付と記録を使う。プランとフードはプロフィールから開く。</t>
         </is>
       </c>
     </row>
@@ -8516,7 +9188,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>日次バッチ。認証のあと喫煙リセットとカロリー再集計を行い cron_runs に残す</t>
+          <t>日次バッチ。認証のあと喫煙リセット、散歩ログの月次マージ、カロリー再集計を行い cron_runs に残す</t>
         </is>
       </c>
     </row>
@@ -8720,7 +9392,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>日週月年の推移。目安線、期間のスライド、今日へ移動</t>
+          <t>線はカロリー、点線は目安、赤点は期末の体重、棒はおさんぽ距離。日付の文字でその期間の数値。グラフ上の左右スライドで期間移動</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9749,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>画像の全体表示。縦横で画面に合わせ、閉じる</t>
+          <t>画像の全体表示。縦横で画面に合わせ、閉じる。共有は iPhone の共有シート（AirDrop 含む）へ写真ファイルを渡す</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9766,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>カードと散歩ログの切替</t>
+          <t>廃止。カードと散歩ログはメニューから別々に開く。このファイルは無い</t>
         </is>
       </c>
     </row>
@@ -9723,7 +10395,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>メニューを一覧とアイコンのどちらで出すか</t>
+          <t>廃止。メニューはカード型だけ。このファイルは無い</t>
         </is>
       </c>
     </row>
@@ -9876,7 +10548,7 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>おくすりの投与。管理は画面下の固定ボタンで、登録・編集・削除を開く。</t>
+          <t>画面名はお世話。毎日のおくすり（予定時刻と投与）と、毎日ではない手入れ（最後にやった日だけ）。おくすりの管理は画面下の固定ボタン。</t>
         </is>
       </c>
     </row>
@@ -10030,6 +10702,74 @@
       <c r="C115" s="8" t="inlineStr">
         <is>
           <t>メニュー下に出した内容の控え。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>src/components/calorie/household-day.tsx</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>多頭の体重とごはんを、その日にまとめて入れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>src/components/calorie/menu-day-notes.tsx</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>メニューの日付の下に、その日の記録と、時刻を過ぎた未投与のお知らせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/calorie/portraits.ts</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>犬種と人の絵の候補。メニューの絵はここから選ぶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>src/lib/smoking/celebrate.ts</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>達成バッチを開いたとき、未表示のものを大きく出す</t>
         </is>
       </c>
     </row>
@@ -10376,7 +11116,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>ごはん、体重、おくすりは、暮らし帳の日付と記録を渡す。このときは取り直さない。</t>
+          <t>ごはん、体重、お世話は、暮らし帳の日付と記録を渡す。このときは取り直さない。</t>
         </is>
       </c>
     </row>
@@ -10503,7 +11243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10576,6 +11316,23 @@
       <c r="C4" s="8" t="inlineStr">
         <is>
           <t>メニューを犬と人に分け、日付と記録を画面へ渡す。一覧は戻ったとき取り直さない。ログイン確認は遷移のたびには行わない。メニュー表示中に先読みする。おくすりの管理は画面下に固定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>お世話（おくすりと手入れ）、最後に会った日の一つ前、写真の共有、グラフの系列（カロリー線・体重の赤点・おさんぽ棒）、散歩の100m切れと700mの月次地図。コードコメントと本書を実装に合わせた。</t>
         </is>
       </c>
     </row>
@@ -10826,7 +11583,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>犬の絵と人の絵で切り替える。犬はごはん、体重、おくすり、おさんぽメモ、おさんぽログ、通院履歴。人は喫煙管理、カップ麺。日付は暮らし帳とごはん・体重・おくすりで共有。プランとフードはプロフィールから開く。</t>
+          <t>犬の絵と人の絵で切り替える。犬はごはん、体重、お世話、おさんぽメモ、おさんぽログ、通院履歴。人は喫煙管理、カップ麺。日付は暮らし帳とごはん・体重・お世話で共有。プランとフードはプロフィールから開く。</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -10843,7 +11600,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ごはん・体重・おくすり</t>
+          <t>ごはん・体重・お世話</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -10892,7 +11649,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>カードの追加・編集・削除。画像は最大3枚。一覧の検索はボタンを押すまで絞り込まない</t>
+          <t>カードの追加・編集・削除。画像は最大3枚。一覧の検索はボタンを押すまで絞り込まない。最後に会った日は一つ前を残し、戻せる。同じ飼い主で日付が違う犬だけ更新確認する。写真は共有シートへ渡せる</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -11024,7 +11781,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>0時に喫煙残数を戻し、週・月・年のカロリーを再集計する</t>
+          <t>0時に喫煙残数を戻し、散歩ログの月次地図を作り、週・月・年のカロリーを再集計する</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -11230,7 +11987,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>ごはん・体重・おくすり</t>
+          <t>ごはん・体重・お世話</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -11586,7 +12343,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>ごはん・体重・おくすり</t>
+          <t>ごはん・体重・お世話</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -11926,7 +12683,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>1. 暮らし帳で読んだ犬・日付・食事・体重・おくすりをブラウザに残す。2. ごはん、体重、おくすりを開くときはそれを渡す。3. どちらかで日付や保存内容が変われば、残している内容も更新する。4. ブラウザを開き直したときだけ取り直す。</t>
+          <t>1. 暮らし帳で読んだ犬・日付・食事・体重・おくすりをブラウザに残す。2. ごはん、体重、お世話を開くときはそれを渡す。3. どちらかで日付や保存内容が変われば、残している内容も更新する。4. ブラウザを開き直したときだけ取り直す。</t>
         </is>
       </c>
     </row>
@@ -12069,12 +12826,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>失敗の分離</t>
+          <t>散歩の月次</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>喫煙リセットが失敗してもカロリー集計は続ける。失敗文は cron_runs の log に残す。</t>
+          <t>喫煙リセットのあと、増減した月だけ散歩ログを作り直す（walk_month_tracks）。700m四方で分け、点の間隔が100m以上なら線を切る。ここが失敗してもカロリー集計は続ける。ログは cron_runs に残す。</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -12749,6 +13506,106 @@
       <c r="D27" s="8" t="inlineStr">
         <is>
           <t>timestamptz は UTC。date は日本時間の暦日</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>app_settings</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>アプリ共通の設定</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>おくすり機能の追加日。この日以前の投与は「—」</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>予定時刻 due_time。未設定の薬は案内を出さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicine_doses</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>おくすりの投与日</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1薬1日1回。given_on は日本時間の暦日</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>最後にやった日だけ。未完了の案内は出さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>700m四方で地域を分け、点間隔100m超は線を切る</t>
         </is>
       </c>
     </row>

--- a/docs/暮らし帳_詳細設計書.xlsx
+++ b/docs/暮らし帳_詳細設計書.xlsx
@@ -10773,6 +10773,57 @@
         </is>
       </c>
     </row>
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>src/routes/checks.tsx</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>チェックリスト画面。ログイン必須。中身は ChecksApp</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>src/components/checks/checks-app.tsx</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>リストと雛形。チェックは保存まで画面だけ。全部済みの保存は削除確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>src/lib/checks/api.ts</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>雛形とリストの保存。全部済みリストの日次削除</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C115"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -11332,7 +11383,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>お世話（おくすりと手入れ）、最後に会った日の一つ前、写真の共有、グラフの系列（カロリー線・体重の赤点・おさんぽ棒）、散歩の100m切れと700mの月次地図。コードコメントと本書を実装に合わせた。</t>
+          <t>お世話（おくすりと手入れ）、最後に会った日の一つ前、写真の共有、グラフの系列（カロリー線・体重の赤点・おさんぽ棒）、散歩の100m切れと700mの月次地図。コードコメントと本書を実装に合わせた。人のチェックリスト（旅行の雛形、保存で一括、全部済みは削除確認と日次削除）を追加。</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11634,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>犬の絵と人の絵で切り替える。犬はごはん、体重、お世話、おさんぽメモ、おさんぽログ、通院履歴。人は喫煙管理、カップ麺。日付は暮らし帳とごはん・体重・お世話で共有。プランとフードはプロフィールから開く。</t>
+          <t>犬の絵と人の絵で切り替える。犬はごはん、体重、お世話、おさんぽメモ、おさんぽログ、通院履歴。人は喫煙管理、カップ麺、チェックリスト。日付は暮らし帳とごはん・体重・お世話で共有。プランとフードはプロフィールから開く。</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -11781,7 +11832,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>0時に喫煙残数を戻し、散歩ログの月次地図を作り、週・月・年のカロリーを再集計する</t>
+          <t>0時に喫煙残数を戻し、散歩ログの月次地図を作り、全部済みのチェックリストを消し、週・月・年のカロリーを再集計する</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -11809,6 +11860,28 @@
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>なし（ブラウザ内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>チェックリスト</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>人のメニュー。雛形（最初は旅行。あとから追加できる）から作るか、名前だけ作る。チェックと項目は保存まで画面だけ。全部チェック済みで保存すると削除確認。項目が1件以上すべて済みのリストは日次でも消す。履歴は残さない。</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>check_templates, check_template_items, check_lists, check_items</t>
         </is>
       </c>
     </row>
@@ -12238,6 +12311,28 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>/checks</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>チェックリスト</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>リスト作成、雛形の管理、項目のチェック。保存でまとめて書く。全部済みなら削除確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D18"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -13609,6 +13704,86 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>check_templates</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>チェックリストの雛形</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>無ければ旅行を1件作る。消したあとは戻さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>check_template_items</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>雛形の項目</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>リスト作成時にコピーする</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>check_lists</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>今のチェックリスト</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>履歴は持たない。全部済みは日次で削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>check_items</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>チェック項目</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>保存時にリスト単位で入れ直す</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D27"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>

--- a/docs/暮らし帳_詳細設計書.xlsx
+++ b/docs/暮らし帳_詳細設計書.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
     <row r="15" ht="64" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>テーブル定義は 2026-10-01 時点の本番データベースに基づく。画面と遷移は 2026-10-14 の実装に合わせた。
+          <t>テーブル定義と画面遷移は 2026-10-28 の実装（migrations と画面）に合わせた。
 日時列（timestamptz）は UTC で保存する。日付だけの列（date）は日本時間の暦日である。
 画面項目は主要画面に限る。認証テーブルのパスワード列は値を本書に記載しない。</t>
         </is>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8536,6 +8536,1686 @@
       <c r="H237" s="8" t="inlineStr">
         <is>
           <t>区切りの一辺。いまは700</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="32" customHeight="1">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C238" s="7" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H238" s="7" t="inlineStr">
+        <is>
+          <t>ログインした人。他人の薬は触らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="32" customHeight="1">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G239" s="8" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="H239" s="8" t="inlineStr">
+        <is>
+          <t>補足。空文字可</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="32" customHeight="1">
+      <c r="A240" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C240" s="7" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H240" s="7" t="inlineStr">
+        <is>
+          <t>画面の並び</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="32" customHeight="1">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G241" s="8" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H241" s="8" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="32" customHeight="1">
+      <c r="A242" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicines</t>
+        </is>
+      </c>
+      <c r="B242" s="7" t="inlineStr">
+        <is>
+          <t>毎日のおくすり</t>
+        </is>
+      </c>
+      <c r="C242" s="7" t="inlineStr">
+        <is>
+          <t>tracked_from</t>
+        </is>
+      </c>
+      <c r="D242" s="7" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="inlineStr">
+        <is>
+          <t>日本時間の今日</t>
+        </is>
+      </c>
+      <c r="H242" s="7" t="inlineStr">
+        <is>
+          <t>この日より前の投与欄は「—」。機能追加時の既存薬は 2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="32" customHeight="1">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicine_doses</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>おくすりの投与日</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E243" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G243" s="8" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="H243" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="32" customHeight="1">
+      <c r="A244" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicine_doses</t>
+        </is>
+      </c>
+      <c r="B244" s="7" t="inlineStr">
+        <is>
+          <t>おくすりの投与日</t>
+        </is>
+      </c>
+      <c r="C244" s="7" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H244" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="32" customHeight="1">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>dog_medicine_doses</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>おくすりの投与日</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>dog_id</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E245" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G245" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H245" s="8" t="inlineStr">
+        <is>
+          <t>dogs.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="32" customHeight="1">
+      <c r="A246" s="7" t="inlineStr">
+        <is>
+          <t>dog_medicine_doses</t>
+        </is>
+      </c>
+      <c r="B246" s="7" t="inlineStr">
+        <is>
+          <t>おくすりの投与日</t>
+        </is>
+      </c>
+      <c r="C246" s="7" t="inlineStr">
+        <is>
+          <t>given_at</t>
+        </is>
+      </c>
+      <c r="D246" s="7" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H246" s="7" t="inlineStr">
+        <is>
+          <t>記録した時刻。UTC。日の判定は given_on</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="32" customHeight="1">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E247" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G247" s="8" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="H247" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="32" customHeight="1">
+      <c r="A248" s="7" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B248" s="7" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C248" s="7" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H248" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="32" customHeight="1">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>dog_id</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G249" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H249" s="8" t="inlineStr">
+        <is>
+          <t>dogs.id。犬を消すと消える</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="32" customHeight="1">
+      <c r="A250" s="7" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B250" s="7" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C250" s="7" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D250" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E250" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F250" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G250" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H250" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="32" customHeight="1">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>dog_cares</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>毎日ではない手入れ</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D251" s="8" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E251" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G251" s="8" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H251" s="8" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="32" customHeight="1">
+      <c r="A252" s="7" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C252" s="7" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D252" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E252" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H252" s="7" t="inlineStr">
+        <is>
+          <t>year_month と組む主キー</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="32" customHeight="1">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>distance_m</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E253" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G253" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H253" s="8" t="inlineStr">
+        <is>
+          <t>その月の距離合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="32" customHeight="1">
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C254" s="7" t="inlineStr">
+        <is>
+          <t>elapsed_sec</t>
+        </is>
+      </c>
+      <c r="D254" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E254" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H254" s="7" t="inlineStr">
+        <is>
+          <t>その月の時間合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="32" customHeight="1">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>log_count</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E255" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F255" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G255" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H255" s="8" t="inlineStr">
+        <is>
+          <t>その月のログ件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="32" customHeight="1">
+      <c r="A256" s="7" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B256" s="7" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C256" s="7" t="inlineStr">
+        <is>
+          <t>polylines</t>
+        </is>
+      </c>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="E256" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H256" s="7" t="inlineStr">
+        <is>
+          <t>初期の軌跡。今の地図は regions</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="32" customHeight="1">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>walk_month_tracks</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>散歩ログの月次地図</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>computed_at</t>
+        </is>
+      </c>
+      <c r="D257" s="8" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E257" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F257" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G257" s="8" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H257" s="8" t="inlineStr">
+        <is>
+          <t>最後に作り直した時刻。UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="32" customHeight="1">
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>check_templates</t>
+        </is>
+      </c>
+      <c r="B258" s="7" t="inlineStr">
+        <is>
+          <t>チェックリストの雛形</t>
+        </is>
+      </c>
+      <c r="C258" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D258" s="7" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E258" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F258" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="inlineStr">
+        <is>
+          <t>gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="H258" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="32" customHeight="1">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>check_templates</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>チェックリストの雛形</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D259" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E259" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F259" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G259" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H259" s="8" t="inlineStr">
+        <is>
+          <t>この人の雛形だけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="32" customHeight="1">
+      <c r="A260" s="7" t="inlineStr">
+        <is>
+          <t>check_templates</t>
+        </is>
+      </c>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>チェックリストの雛形</t>
+        </is>
+      </c>
+      <c r="C260" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E260" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H260" s="7" t="inlineStr">
+        <is>
+          <t>40文字まで（画面側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="32" customHeight="1">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>check_templates</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>チェックリストの雛形</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E261" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F261" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G261" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H261" s="8" t="inlineStr">
+        <is>
+          <t>追加のたびに最大+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="32" customHeight="1">
+      <c r="A262" s="7" t="inlineStr">
+        <is>
+          <t>check_templates</t>
+        </is>
+      </c>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>チェックリストの雛形</t>
+        </is>
+      </c>
+      <c r="C262" s="7" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D262" s="7" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E262" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F262" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G262" s="7" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H262" s="7" t="inlineStr">
+        <is>
+          <t>UTC。雛形が0件のときだけ旅行を自動作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="32" customHeight="1">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>check_template_items</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
+        <is>
+          <t>雛形の項目</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E263" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F263" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G263" s="8" t="inlineStr">
+        <is>
+          <t>gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="H263" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="32" customHeight="1">
+      <c r="A264" s="7" t="inlineStr">
+        <is>
+          <t>check_template_items</t>
+        </is>
+      </c>
+      <c r="B264" s="7" t="inlineStr">
+        <is>
+          <t>雛形の項目</t>
+        </is>
+      </c>
+      <c r="C264" s="7" t="inlineStr">
+        <is>
+          <t>template_id</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E264" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F264" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G264" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H264" s="7" t="inlineStr">
+        <is>
+          <t>check_templates.id。雛形を消すと項目も消える</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="32" customHeight="1">
+      <c r="A265" s="8" t="inlineStr">
+        <is>
+          <t>check_template_items</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
+          <t>雛形の項目</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E265" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F265" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G265" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H265" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="32" customHeight="1">
+      <c r="A266" s="7" t="inlineStr">
+        <is>
+          <t>check_template_items</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t>雛形の項目</t>
+        </is>
+      </c>
+      <c r="C266" s="7" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D266" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E266" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F266" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G266" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H266" s="7" t="inlineStr">
+        <is>
+          <t>1行1項目。80文字まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="32" customHeight="1">
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>check_template_items</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
+        <is>
+          <t>雛形の項目</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D267" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E267" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F267" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G267" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H267" s="8" t="inlineStr">
+        <is>
+          <t>画面の行順</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="32" customHeight="1">
+      <c r="A268" s="7" t="inlineStr">
+        <is>
+          <t>check_lists</t>
+        </is>
+      </c>
+      <c r="B268" s="7" t="inlineStr">
+        <is>
+          <t>今のチェックリスト</t>
+        </is>
+      </c>
+      <c r="C268" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D268" s="7" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E268" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F268" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G268" s="7" t="inlineStr">
+        <is>
+          <t>gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="H268" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="32" customHeight="1">
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>check_lists</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>今のチェックリスト</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D269" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E269" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F269" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G269" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H269" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="32" customHeight="1">
+      <c r="A270" s="7" t="inlineStr">
+        <is>
+          <t>check_lists</t>
+        </is>
+      </c>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>今のチェックリスト</t>
+        </is>
+      </c>
+      <c r="C270" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D270" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E270" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F270" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G270" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H270" s="7" t="inlineStr">
+        <is>
+          <t>40文字まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="32" customHeight="1">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>check_lists</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>今のチェックリスト</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D271" s="8" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E271" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F271" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G271" s="8" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H271" s="8" t="inlineStr">
+        <is>
+          <t>新しい順に一覧。履歴は残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="32" customHeight="1">
+      <c r="A272" s="7" t="inlineStr">
+        <is>
+          <t>check_items</t>
+        </is>
+      </c>
+      <c r="B272" s="7" t="inlineStr">
+        <is>
+          <t>チェック項目</t>
+        </is>
+      </c>
+      <c r="C272" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D272" s="7" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E272" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F272" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G272" s="7" t="inlineStr">
+        <is>
+          <t>gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="H272" s="7" t="inlineStr">
+        <is>
+          <t>保存のたびに作り直す。画面の key は保存後の id</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="32" customHeight="1">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>check_items</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>チェック項目</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>list_id</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E273" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F273" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G273" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H273" s="8" t="inlineStr">
+        <is>
+          <t>check_lists.id。リスト削除で消える</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="32" customHeight="1">
+      <c r="A274" s="7" t="inlineStr">
+        <is>
+          <t>check_items</t>
+        </is>
+      </c>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>チェック項目</t>
+        </is>
+      </c>
+      <c r="C274" s="7" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E274" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F274" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G274" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H274" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="32" customHeight="1">
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>check_items</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>チェック項目</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D275" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E275" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F275" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G275" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H275" s="8" t="inlineStr">
+        <is>
+          <t>80文字まで。100件まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="32" customHeight="1">
+      <c r="A276" s="7" t="inlineStr">
+        <is>
+          <t>check_items</t>
+        </is>
+      </c>
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>チェック項目</t>
+        </is>
+      </c>
+      <c r="C276" s="7" t="inlineStr">
+        <is>
+          <t>checked</t>
+        </is>
+      </c>
+      <c r="D276" s="7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E276" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F276" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G276" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H276" s="7" t="inlineStr">
+        <is>
+          <t>雛形からコピーした直後は false</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="32" customHeight="1">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>check_items</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
+        <is>
+          <t>チェック項目</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D277" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E277" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F277" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G277" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H277" s="8" t="inlineStr">
+        <is>
+          <t>保存時の並び</t>
         </is>
       </c>
     </row>
@@ -8742,7 +10422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9188,7 +10868,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>日次バッチ。認証のあと喫煙リセット、散歩ログの月次マージ、カロリー再集計を行い cron_runs に残す</t>
+          <t>日次バッチ。認証のあと喫煙リセット、散歩ログの月次、全部済みチェックリストの削除、カロリー再集計。結果は cron_runs</t>
         </is>
       </c>
     </row>
@@ -9715,7 +11395,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>一覧の1枚。サムネ、虹、今日会った</t>
+          <t>一覧の1枚。サムネ、虹、今日会った。最後に会った日の一つ前があれば、その日付に戻す</t>
         </is>
       </c>
     </row>
@@ -10599,7 +12279,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>暮らし帳表示中に、メニュー先の画面とデータを先読みする。</t>
+          <t>暮らし帳表示中に、メニュー先の画面とデータを先読みする。チェックリストを含む。</t>
         </is>
       </c>
     </row>
@@ -11053,7 +12733,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>メニューを出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺と、各画面の部品を裏で読む。</t>
+          <t>メニューを出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺、チェックリストと、各画面の部品を裏で読む。</t>
         </is>
       </c>
     </row>
@@ -11184,7 +12864,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺は、先読みか前回の内容があればそれを出す。</t>
+          <t>おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺、チェックリストは、先読みか前回の内容があればそれを出す。</t>
         </is>
       </c>
     </row>
@@ -11294,7 +12974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11384,6 +13064,23 @@
       <c r="C5" s="7" t="inlineStr">
         <is>
           <t>お世話（おくすりと手入れ）、最後に会った日の一つ前、写真の共有、グラフの系列（カロリー線・体重の赤点・おさんぽ棒）、散歩の100m切れと700mの月次地図。コードコメントと本書を実装に合わせた。人のチェックリスト（旅行の雛形、保存で一括、全部済みは削除確認と日次削除）を追加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>日次バッチの手順にチェックリスト削除を足す。先読みと人のメニュー遷移にチェックリストを入れる。テーブル定義にチェックリストの列と、おくすり・手入れ・月次地図の不足列を足し、列数を定義に合わせる。画面の処理コメントを、直す場所が分かる粒度まで足した。動きは変えていない。</t>
         </is>
       </c>
     </row>
@@ -11854,7 +13551,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>暮らし帳を出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺を裏で読む。一度開いた内容は、戻ったときに再取得しない。ログインと表示設定も、遷移のたびには取り直さない。</t>
+          <t>暮らし帳を出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺、チェックリストを裏で読む。一度開いた内容は、戻ったときに再取得しない。ログインと表示設定も、遷移のたびには取り直さない。</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -12472,7 +14169,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>喫煙管理、カップ麺</t>
+          <t>喫煙管理、カップ麺、チェックリスト</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -12570,7 +14267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12795,7 +14492,24 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>1. 暮らし帳を出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺を裏で読む。2. 戻ったときは残している内容を出す。3. 保存、削除、取り込みのあとだけ取り直す。4. ログインとメニュー下の表示設定は、最初の1回だけサーバーへ聞く。</t>
+          <t>1. 暮らし帳を出したあと、おさんぽメモ、おさんぽログ、通院履歴、喫煙管理、カップ麺、チェックリストを裏で読む。2. 戻ったときは残している内容を出す。3. 保存、削除、取り込みのあとだけ取り直す。4. ログインとメニュー下の表示設定は、最初の1回だけサーバーへ聞く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>チェックリスト</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>1. チェックと項目の追加・削除は画面の下書きだけ。DBは変えない。2. 保存で、そのリストの check_items を消し、今の並びで入れ直す。3. 項目が1件以上かつ全部チェックなら、削除するか確認する。はいならリストを消す（項目は保存しない）。いいえなら保存せず画面に残す。4. 未保存のまま一覧へ戻ると、捨てるか確認する。5. 全部チェックのまま保存して残したリストは、日次バッチで消す。項目が0件のリストは消さない。履歴テーブルは無い。</t>
         </is>
       </c>
     </row>
@@ -12820,7 +14534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12930,20 +14644,20 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row ht="48" customHeight="1" r="7">
+      <c r="A7" t="inlineStr" s="8">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>dogs の全頭。基準日は今日（日本時間）。</t>
+      <c r="B7" t="inlineStr" s="8">
+        <is>
+          <t>チェックリスト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="8">
+        <is>
+          <t>散歩の月次のあと。項目が1件以上あり、全部チェック済みの check_lists だけ消す（purgeCheckedLists）。項目が空のリストと、途中のリストは残す。履歴は残さない。ここが失敗してもカロリー集計は続ける。</t>
         </is>
       </c>
     </row>
@@ -12955,12 +14669,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>読込</t>
+          <t>対象</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>約5年分（366日×5）の calorie_logs を日別に合計し、dog_weight_logs を日別に読む。カロリーは小数第1位で切り捨て。</t>
+          <t>dogs の全頭。基準日は今日（日本時間）。</t>
         </is>
       </c>
     </row>
@@ -12972,12 +14686,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>期間</t>
+          <t>読込</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>週は月曜〜日曜、月は1日〜月末、年は1月1日〜12月31日。進行中の期間の終わりは今日まで。</t>
+          <t>約5年分（366日×5）の calorie_logs を日別に合計し、dog_weight_logs を日別に読む。カロリーは小数第1位で切り捨て。</t>
         </is>
       </c>
     </row>
@@ -12989,12 +14703,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>値</t>
+          <t>期間</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>カロリーは期間内の日別合計を足して再び小数第1位で切り捨てる。体重は期間の最終日、無ければ期間内で最も新しい記録。</t>
+          <t>週は月曜〜日曜、月は1日〜月末、年は1月1日〜12月31日。進行中の期間の終わりは今日まで。</t>
         </is>
       </c>
     </row>
@@ -13006,12 +14720,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>保存</t>
+          <t>値</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>week / month / year だけ calorie_period_stats へ upsert する。日別テーブルは作らない。目安カロリーは更新しない。</t>
+          <t>カロリーは期間内の日別合計を足して再び小数第1位で切り捨てる。体重は期間の最終日、無ければ期間内で最も新しい記録。</t>
         </is>
       </c>
     </row>
@@ -13023,12 +14737,29 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
+          <t>保存</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>week / month / year だけ calorie_period_stats へ upsert する。日別テーブルは作らない。目安カロリーは更新しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>終了</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>成功なら cron_runs.ok を true にして HTTP 200。カロリー集計が失敗なら ok を false にして HTTP 500。</t>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>成功なら cron_runs.ok を true にして HTTP 200。カロリー集計が失敗なら ok を false にして HTTP 500。応答には smoking、walks、checks を含める。</t>
         </is>
       </c>
     </row>
@@ -13095,8 +14826,10 @@
           <t>適用済みマイグレーション</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
-        <v>2</v>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
@@ -13115,8 +14848,10 @@
           <t>認証アカウント（パスワード）</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
-        <v>13</v>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
@@ -13135,8 +14870,10 @@
           <t>カロリー明細</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
-        <v>11</v>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -13155,8 +14892,10 @@
           <t>期間ごとの目安カロリー</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>8</v>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
@@ -13175,8 +14914,10 @@
           <t>週・月・年のカロリー集計</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>9</v>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -13195,8 +14936,10 @@
           <t>定番フード</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>7</v>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
@@ -13215,8 +14958,10 @@
           <t>日次バッチの実行記録</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>10</v>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -13235,8 +14980,10 @@
           <t>カップ麺の品名</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>6</v>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
@@ -13255,8 +15002,10 @@
           <t>カップ麺の在庫</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>8</v>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -13275,8 +15024,10 @@
           <t>犬ネタの取得キャッシュ</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>3</v>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
@@ -13295,8 +15046,10 @@
           <t>犬種マスタ</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>5</v>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -13315,8 +15068,10 @@
           <t>毛色マスタ</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
-        <v>5</v>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
@@ -13335,8 +15090,10 @@
           <t>フード</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>10</v>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -13355,8 +15112,10 @@
           <t>体重記録</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
-        <v>8</v>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
@@ -13375,8 +15134,10 @@
           <t>愛犬</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
-        <v>9</v>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -13395,8 +15156,10 @@
           <t>お散歩メモ</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
-        <v>20</v>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
@@ -13415,8 +15178,10 @@
           <t>ログインセッション</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>8</v>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -13435,8 +15200,10 @@
           <t>喫煙の達成バッチ</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
-        <v>19</v>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
@@ -13455,8 +15222,10 @@
           <t>喫煙の上限と残数</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>8</v>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -13475,8 +15244,10 @@
           <t>ログインユーザー</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
-        <v>7</v>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
@@ -13495,8 +15266,10 @@
           <t>表示済みの犬の豆知識</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>4</v>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -13515,8 +15288,10 @@
           <t>メニュー下の表示設定</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
-        <v>8</v>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
@@ -13535,8 +15310,10 @@
           <t>パスワード再設定トークン</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>6</v>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
@@ -13555,8 +15332,10 @@
           <t>次回に先生へ伝えるメモ</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
-        <v>3</v>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
@@ -13575,8 +15354,10 @@
           <t>通院</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>14</v>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -13595,8 +15376,10 @@
           <t>散歩ログ</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n">
-        <v>9</v>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
@@ -13615,8 +15398,10 @@
           <t>アプリ共通の設定</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>2</v>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -13635,8 +15420,10 @@
           <t>毎日のおくすり</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n">
-        <v>8</v>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
@@ -13655,8 +15442,10 @@
           <t>おくすりの投与日</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>6</v>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -13675,8 +15464,10 @@
           <t>毎日ではない手入れ</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n">
-        <v>6</v>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
@@ -13695,8 +15486,10 @@
           <t>散歩ログの月次地図</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>8</v>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -13715,8 +15508,10 @@
           <t>チェックリストの雛形</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n">
-        <v>4</v>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
@@ -13735,8 +15530,10 @@
           <t>雛形の項目</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>4</v>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -13755,8 +15552,10 @@
           <t>今のチェックリスト</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n">
-        <v>4</v>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
@@ -13775,8 +15574,10 @@
           <t>チェック項目</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>5</v>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
